--- a/Team-Data/2011-12/2-12-2011-12.xlsx
+++ b/Team-Data/2011-12/2-12-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,91 +728,91 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="H2" t="n">
         <v>49.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.449</v>
+        <v>0.452</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.392</v>
+        <v>0.391</v>
       </c>
       <c r="O2" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R2" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S2" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U2" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V2" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X2" t="n">
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
         <v>17.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.5</v>
+        <v>95.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
       </c>
       <c r="AF2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
         <v>7</v>
@@ -757,25 +824,25 @@
         <v>12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
         <v>12</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="n">
         <v>17</v>
       </c>
-      <c r="AN2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>20</v>
-      </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>23</v>
@@ -784,22 +851,22 @@
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -808,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -843,91 +910,91 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.556</v>
+        <v>0.538</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J3" t="n">
         <v>75.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.764</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T3" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="U3" t="n">
         <v>22.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y3" t="n">
         <v>5.4</v>
       </c>
-      <c r="Y3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="Z3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>90.2</v>
+        <v>90</v>
       </c>
       <c r="AC3" t="n">
         <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -945,49 +1012,49 @@
         <v>9</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-14.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1115,7 +1182,7 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1163,7 +1230,7 @@
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>23</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J5" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.462</v>
+        <v>0.465</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
         <v>15.6</v>
       </c>
       <c r="P5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="R5" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T5" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U5" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V5" t="n">
         <v>13.9</v>
@@ -1267,22 +1334,22 @@
         <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Z5" t="n">
         <v>17.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1291,28 +1358,28 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
         <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL5" t="n">
         <v>21</v>
       </c>
       <c r="AM5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
         <v>8</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
@@ -1488,7 +1555,7 @@
         <v>12</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>13</v>
@@ -1524,7 +1591,7 @@
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1661,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI7" t="n">
         <v>16</v>
@@ -1673,7 +1740,7 @@
         <v>16</v>
       </c>
       <c r="AL7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AM7" t="n">
         <v>5</v>
@@ -1682,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1855,13 +1922,13 @@
         <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
         <v>29</v>
@@ -1879,7 +1946,7 @@
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -1888,7 +1955,7 @@
         <v>25</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
         <v>18</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -1935,70 +2002,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>0.276</v>
+        <v>0.286</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
       </c>
       <c r="I9" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="J9" t="n">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.428</v>
+        <v>0.432</v>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.333</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
         <v>20.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.778</v>
+        <v>0.772</v>
       </c>
       <c r="R9" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S9" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="T9" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V9" t="n">
         <v>16.3</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z9" t="n">
         <v>19.1</v>
@@ -2007,13 +2074,13 @@
         <v>18.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>87.2</v>
+        <v>87.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.5</v>
+        <v>-8.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>26</v>
@@ -2031,10 +2098,10 @@
         <v>27</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
         <v>25</v>
@@ -2043,10 +2110,10 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP9" t="n">
         <v>21</v>
@@ -2064,7 +2131,7 @@
         <v>29</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV9" t="n">
         <v>27</v>
@@ -2076,7 +2143,7 @@
         <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
         <v>9</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>0.417</v>
+        <v>0.391</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J10" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.396</v>
+        <v>0.389</v>
       </c>
       <c r="O10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q10" t="n">
         <v>0.735</v>
       </c>
       <c r="R10" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="S10" t="n">
         <v>29.8</v>
       </c>
       <c r="T10" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="U10" t="n">
         <v>23.1</v>
@@ -2174,34 +2241,34 @@
         <v>15.1</v>
       </c>
       <c r="W10" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y10" t="n">
         <v>4</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="AA10" t="n">
         <v>17.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.3</v>
+        <v>99</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AD10" t="n">
         <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
         <v>22</v>
@@ -2210,13 +2277,13 @@
         <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2225,10 +2292,10 @@
         <v>6</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>24</v>
@@ -2237,10 +2304,10 @@
         <v>22</v>
       </c>
       <c r="AR10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
         <v>27</v>
@@ -2249,13 +2316,13 @@
         <v>2</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY10" t="n">
         <v>3</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -2299,91 +2366,91 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
         <v>16</v>
       </c>
       <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="H11" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>85</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R11" t="n">
         <v>12</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="H11" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="O11" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="P11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="R11" t="n">
-        <v>12.1</v>
-      </c>
       <c r="S11" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T11" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U11" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V11" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X11" t="n">
         <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA11" t="n">
         <v>17.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>11</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
@@ -2398,13 +2465,13 @@
         <v>1</v>
       </c>
       <c r="AK11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL11" t="n">
         <v>11</v>
       </c>
-      <c r="AL11" t="n">
-        <v>7</v>
-      </c>
       <c r="AM11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>15</v>
@@ -2413,16 +2480,16 @@
         <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
         <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
         <v>4</v>
@@ -2431,16 +2498,16 @@
         <v>13</v>
       </c>
       <c r="AV11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX11" t="n">
         <v>14</v>
       </c>
-      <c r="AW11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>15</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>13</v>
       </c>
       <c r="AZ11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -2559,34 +2626,34 @@
         <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG12" t="n">
         <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>23</v>
       </c>
       <c r="AM12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN12" t="n">
         <v>9</v>
@@ -2598,13 +2665,13 @@
         <v>9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2759,7 +2826,7 @@
         <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK13" t="n">
         <v>7</v>
@@ -2789,7 +2856,7 @@
         <v>22</v>
       </c>
       <c r="AT13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
         <v>8</v>
@@ -2801,13 +2868,13 @@
         <v>12</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
@@ -2866,52 +2933,52 @@
         <v>79</v>
       </c>
       <c r="K14" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="M14" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.291</v>
+        <v>0.284</v>
       </c>
       <c r="O14" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R14" t="n">
         <v>11.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="T14" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U14" t="n">
         <v>20.8</v>
       </c>
       <c r="V14" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W14" t="n">
         <v>5.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>3.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
         <v>19.9</v>
@@ -2923,16 +2990,16 @@
         <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
         <v>14</v>
@@ -2941,10 +3008,10 @@
         <v>17</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL14" t="n">
         <v>24</v>
@@ -2968,7 +3035,7 @@
         <v>11</v>
       </c>
       <c r="AS14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,13 +3044,13 @@
         <v>16</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>21</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
@@ -3045,7 +3112,7 @@
         <v>36.1</v>
       </c>
       <c r="J15" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>0.438</v>
@@ -3054,73 +3121,73 @@
         <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.307</v>
+        <v>0.311</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P15" t="n">
         <v>22.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="S15" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T15" t="n">
         <v>42.4</v>
       </c>
       <c r="U15" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF15" t="n">
         <v>16</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
@@ -3147,10 +3214,10 @@
         <v>14</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
         <v>14</v>
@@ -3159,13 +3226,13 @@
         <v>25</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY15" t="n">
         <v>25</v>
@@ -3177,10 +3244,10 @@
         <v>15</v>
       </c>
       <c r="BB15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.75</v>
+        <v>0.741</v>
       </c>
       <c r="H16" t="n">
         <v>48.9</v>
@@ -3227,73 +3294,73 @@
         <v>38.2</v>
       </c>
       <c r="J16" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="L16" t="n">
         <v>5.7</v>
       </c>
       <c r="M16" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="O16" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="P16" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.772</v>
       </c>
       <c r="R16" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S16" t="n">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
       <c r="T16" t="n">
-        <v>42.5</v>
+        <v>42.1</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W16" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y16" t="n">
         <v>4.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>103</v>
+        <v>102.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="n">
         <v>3</v>
@@ -3302,10 +3369,10 @@
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -3326,28 +3393,28 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS16" t="n">
         <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW16" t="n">
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
@@ -3481,7 +3548,7 @@
         <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
         <v>13</v>
@@ -3490,7 +3557,7 @@
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>12</v>
@@ -3502,7 +3569,7 @@
         <v>17</v>
       </c>
       <c r="AO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP17" t="n">
         <v>23</v>
@@ -3511,10 +3578,10 @@
         <v>4</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3529,16 +3596,16 @@
         <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3718,10 @@
         <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>19</v>
@@ -3669,16 +3736,16 @@
         <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>15</v>
       </c>
       <c r="AM18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN18" t="n">
         <v>20</v>
@@ -3693,7 +3760,7 @@
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
         <v>7</v>
@@ -3726,7 +3793,7 @@
         <v>11</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-7.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
@@ -3869,19 +3936,19 @@
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
       </c>
       <c r="AT19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU19" t="n">
         <v>19</v>
@@ -3890,16 +3957,16 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
         <v>13</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>29</v>
@@ -4027,13 +4094,13 @@
         <v>29</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
         <v>17</v>
@@ -4060,7 +4127,7 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4081,7 +4148,7 @@
         <v>22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>0.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF21" t="n">
         <v>19</v>
@@ -4209,7 +4276,7 @@
         <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
@@ -4218,10 +4285,10 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
@@ -4230,22 +4297,22 @@
         <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP21" t="n">
         <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS21" t="n">
         <v>18</v>
       </c>
-      <c r="AS21" t="n">
-        <v>17</v>
-      </c>
       <c r="AT21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4269,10 +4336,10 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4388,10 +4455,10 @@
         <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>11</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>7</v>
@@ -4573,7 +4640,7 @@
         <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4618,7 +4685,7 @@
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>9.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>4</v>
@@ -4755,10 +4822,10 @@
         <v>5</v>
       </c>
       <c r="AH24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
@@ -4767,13 +4834,13 @@
         <v>8</v>
       </c>
       <c r="AL24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>20</v>
       </c>
       <c r="AN24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,22 +4852,22 @@
         <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX24" t="n">
         <v>22</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>20</v>
@@ -4943,13 +5010,13 @@
         <v>14</v>
       </c>
       <c r="AJ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM25" t="n">
         <v>13</v>
@@ -4961,13 +5028,13 @@
         <v>29</v>
       </c>
       <c r="AP25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ25" t="n">
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4982,7 +5049,7 @@
         <v>9</v>
       </c>
       <c r="AW25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -4994,7 +5061,7 @@
         <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>5.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
@@ -5143,7 +5210,7 @@
         <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>5</v>
@@ -5155,7 +5222,7 @@
         <v>14</v>
       </c>
       <c r="AT26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
@@ -5167,7 +5234,7 @@
         <v>3</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
         <v>12</v>
@@ -5179,7 +5246,7 @@
         <v>7</v>
       </c>
       <c r="BB26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5301,19 +5368,19 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK27" t="n">
         <v>30</v>
       </c>
       <c r="AL27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM27" t="n">
         <v>9</v>
@@ -5334,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
@@ -5364,7 +5431,7 @@
         <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5483,7 +5550,7 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI28" t="n">
         <v>7</v>
@@ -5498,7 +5565,7 @@
         <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN28" t="n">
         <v>7</v>
@@ -5513,7 +5580,7 @@
         <v>25</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>11</v>
@@ -5522,7 +5589,7 @@
         <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -5575,88 +5642,88 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
         <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>0.31</v>
+        <v>0.321</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="J29" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.421</v>
+        <v>0.42</v>
       </c>
       <c r="L29" t="n">
         <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="O29" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R29" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
         <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U29" t="n">
         <v>20.6</v>
       </c>
       <c r="V29" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W29" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF29" t="n">
         <v>25</v>
@@ -5665,7 +5732,7 @@
         <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>30</v>
@@ -5674,19 +5741,19 @@
         <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL29" t="n">
         <v>20</v>
       </c>
       <c r="AM29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO29" t="n">
         <v>16</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>17</v>
       </c>
       <c r="AP29" t="n">
         <v>20</v>
@@ -5695,7 +5762,7 @@
         <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
@@ -5710,13 +5777,13 @@
         <v>19</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -5757,58 +5824,58 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" t="n">
         <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>0.538</v>
+        <v>0.52</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
       </c>
       <c r="I30" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K30" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L30" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M30" t="n">
         <v>12.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.297</v>
+        <v>0.293</v>
       </c>
       <c r="O30" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="P30" t="n">
-        <v>25.9</v>
+        <v>26.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R30" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U30" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V30" t="n">
         <v>14</v>
@@ -5820,31 +5887,31 @@
         <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z30" t="n">
         <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG30" t="n">
         <v>16</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>15</v>
       </c>
       <c r="AH30" t="n">
         <v>5</v>
@@ -5856,7 +5923,7 @@
         <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
@@ -5868,25 +5935,25 @@
         <v>27</v>
       </c>
       <c r="AO30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
         <v>13</v>
       </c>
       <c r="AS30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU30" t="n">
         <v>15</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>14</v>
       </c>
       <c r="AV30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
         <v>22</v>
       </c>
       <c r="G31" t="n">
-        <v>0.214</v>
+        <v>0.185</v>
       </c>
       <c r="H31" t="n">
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J31" t="n">
-        <v>83.5</v>
+        <v>83.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.421</v>
+        <v>0.42</v>
       </c>
       <c r="L31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M31" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.299</v>
+        <v>0.295</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.724</v>
+        <v>0.72</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="T31" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U31" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="V31" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W31" t="n">
         <v>8.4</v>
@@ -6002,22 +6069,22 @@
         <v>7.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="AA31" t="n">
         <v>18.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="AC31" t="n">
-        <v>-9.1</v>
+        <v>-10.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6029,16 +6096,16 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6053,7 +6120,7 @@
         <v>21</v>
       </c>
       <c r="AP31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6062,16 +6129,16 @@
         <v>10</v>
       </c>
       <c r="AS31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
@@ -6080,10 +6147,10 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-12-2011-12</t>
+          <t>2012-02-12</t>
         </is>
       </c>
     </row>
